--- a/SHOO.xlsx
+++ b/SHOO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6233FBB0-234D-411B-865D-FA6D4F342F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BB5C48-CF95-4248-94E8-AE2E8A960AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C42A3123-EC18-4E9E-AA0A-1C921C0157F2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t xml:space="preserve">Steve Madden </t>
   </si>
@@ -197,6 +197,18 @@
   <si>
     <t>Q425</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -206,13 +218,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -275,28 +293,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -653,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>33.92</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -661,10 +682,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="3">
-        <v>72.652392000000006</v>
+        <v>73.085436000000001</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>46</v>
+      <c r="I3" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -676,7 +697,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>2464.3691366400003</v>
+        <v>3217.9517470800001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -687,11 +708,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="3">
-        <f>111.174+0.14</f>
-        <v>111.31400000000001</v>
+        <v>77.156000000000006</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>46</v>
+      <c r="I5" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -699,11 +719,10 @@
         <v>8</v>
       </c>
       <c r="H6" s="3">
-        <f>287.865+5.625</f>
-        <v>293.49</v>
+        <v>286.49700000000001</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>46</v>
+      <c r="I6" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -712,7 +731,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>2646.5451366400002</v>
+        <v>3427.29274708</v>
       </c>
     </row>
   </sheetData>
@@ -730,12 +749,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -772,8 +791,20 @@
       <c r="N2" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O2" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>35</v>
@@ -796,8 +827,11 @@
       <c r="L3" s="12">
         <v>220.13900000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O3" s="12">
+        <v>278.86599999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>36</v>
@@ -820,8 +854,11 @@
       <c r="L4" s="12">
         <v>140.44900000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O4" s="12">
+        <v>164.78100000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>37</v>
@@ -844,8 +881,11 @@
       <c r="L5" s="12">
         <v>195.50200000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="12">
+        <v>206.01300000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>38</v>
@@ -868,8 +908,11 @@
       <c r="L6" s="12">
         <v>2.91</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="12">
+        <v>3.4359999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>19</v>
@@ -892,8 +935,11 @@
       <c r="L7" s="12">
         <v>556.09</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O7" s="12">
+        <v>649.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>20</v>
@@ -916,8 +962,11 @@
       <c r="L8" s="12">
         <v>2.91</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O8" s="12">
+        <v>3.4359999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1" t="s">
         <v>21</v>
@@ -951,7 +1000,7 @@
         <v>624.67499999999995</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" ref="J9:N9" si="1">+J7+J8</f>
+        <f t="shared" ref="J9:O9" si="1">+J7+J8</f>
         <v>0</v>
       </c>
       <c r="K9" s="13">
@@ -970,8 +1019,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O9" s="13">
+        <f t="shared" si="1"/>
+        <v>653.096</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>22</v>
@@ -994,8 +1047,11 @@
       <c r="L10" s="12">
         <v>332.97300000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="12">
+        <v>295.67599999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>23</v>
@@ -1029,7 +1085,7 @@
         <v>259.54399999999998</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" ref="J11:N11" si="3">+J9-J10</f>
+        <f t="shared" ref="J11:O11" si="3">+J9-J10</f>
         <v>0</v>
       </c>
       <c r="K11" s="12">
@@ -1048,8 +1104,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O11" s="12">
+        <f t="shared" si="3"/>
+        <v>357.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>24</v>
@@ -1072,8 +1132,11 @@
       <c r="L12" s="12">
         <v>263.86500000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O12" s="12">
+        <v>258.29300000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1096,8 +1159,11 @@
       <c r="L13" s="12">
         <v>2.42</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="12">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
@@ -1120,8 +1186,11 @@
       <c r="L14" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -1155,7 +1224,7 @@
         <v>74.578000000000003</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" ref="J15:N15" si="5">+J11-SUM(J12:J14)</f>
+        <f t="shared" ref="J15:O15" si="5">+J11-SUM(J12:J14)</f>
         <v>0</v>
       </c>
       <c r="K15" s="12">
@@ -1174,8 +1243,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="12">
+        <f t="shared" si="5"/>
+        <v>98.742000000000019</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -1198,6 +1271,9 @@
       <c r="L16" s="12">
         <f>9.252-3.795</f>
         <v>5.4570000000000007</v>
+      </c>
+      <c r="O16" s="12">
+        <v>-3.605</v>
       </c>
     </row>
     <row r="17" spans="1:88" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -1234,7 +1310,7 @@
         <v>75.978000000000009</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" ref="J17:N17" si="7">+J15+J16</f>
+        <f t="shared" ref="J17:O17" si="7">+J15+J16</f>
         <v>0</v>
       </c>
       <c r="K17" s="12">
@@ -1252,6 +1328,10 @@
       <c r="N17" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
+      </c>
+      <c r="O17" s="12">
+        <f t="shared" si="7"/>
+        <v>95.137000000000015</v>
       </c>
     </row>
     <row r="18" spans="1:88" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -1276,6 +1356,9 @@
       </c>
       <c r="L18" s="12">
         <v>3.911</v>
+      </c>
+      <c r="O18" s="12">
+        <v>23.494</v>
       </c>
     </row>
     <row r="19" spans="1:88" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -1312,7 +1395,7 @@
         <v>56.588000000000008</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" ref="J19:N19" si="9">+J17-J18</f>
+        <f t="shared" ref="J19:O19" si="9">+J17-J18</f>
         <v>0</v>
       </c>
       <c r="K19" s="12">
@@ -1330,6 +1413,10 @@
       <c r="N19" s="12">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="O19" s="12">
+        <f t="shared" si="9"/>
+        <v>71.643000000000015</v>
       </c>
     </row>
     <row r="20" spans="1:88" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -1354,6 +1441,9 @@
       </c>
       <c r="L20" s="12">
         <v>0.76500000000000001</v>
+      </c>
+      <c r="O20" s="12">
+        <v>-0.17899999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:88" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -1390,7 +1480,7 @@
         <v>55.278000000000006</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" ref="J21:N21" si="11">+J19-J20</f>
+        <f t="shared" ref="J21:O21" si="11">+J19-J20</f>
         <v>0</v>
       </c>
       <c r="K21" s="12">
@@ -1408,6 +1498,10 @@
       <c r="N21" s="12">
         <f t="shared" si="11"/>
         <v>0</v>
+      </c>
+      <c r="O21" s="12">
+        <f t="shared" si="11"/>
+        <v>71.822000000000017</v>
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.2">
@@ -1515,7 +1609,7 @@
         <v>0.88305937512852439</v>
       </c>
       <c r="F23" s="7" t="e">
-        <f t="shared" ref="F23:N23" si="13">+F21/F24</f>
+        <f t="shared" ref="F23:O23" si="13">+F21/F24</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G23" s="7">
@@ -1550,7 +1644,10 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O23" s="3"/>
+      <c r="O23" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0092604302797805</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -1653,7 +1750,9 @@
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="O24" s="3">
+        <v>71.162999999999997</v>
+      </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -1856,7 +1955,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="3"/>
+      <c r="O26" s="8">
+        <f t="shared" ref="O26:O32" si="16">+O3/K3-1</f>
+        <v>-5.8346418139762601E-2</v>
+      </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -1948,7 +2050,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:I32" si="16">+I4/E4-1</f>
+        <f t="shared" ref="I27:I32" si="17">+I4/E4-1</f>
         <v>0.54166176066564642</v>
       </c>
       <c r="J27" s="8" t="e">
@@ -1971,7 +2073,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="3"/>
+      <c r="O27" s="8">
+        <f t="shared" si="16"/>
+        <v>0.15092231077088569</v>
+      </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -2063,7 +2168,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.9712202972640256E-2</v>
       </c>
       <c r="J28" s="8" t="e">
@@ -2086,7 +2191,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="3"/>
+      <c r="O28" s="8">
+        <f t="shared" si="16"/>
+        <v>0.83835129925756724</v>
+      </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -2178,7 +2286,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.21448371448371439</v>
       </c>
       <c r="J29" s="8" t="e">
@@ -2201,7 +2309,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="3"/>
+      <c r="O29" s="8">
+        <f t="shared" si="16"/>
+        <v>0.59665427509293667</v>
+      </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -2293,7 +2404,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.12971632056975935</v>
       </c>
       <c r="J30" s="8" t="e">
@@ -2316,7 +2427,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="3"/>
+      <c r="O30" s="8">
+        <f t="shared" si="16"/>
+        <v>0.1782394057114669</v>
+      </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -2408,7 +2522,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.21448371448371439</v>
       </c>
       <c r="J31" s="8" t="e">
@@ -2431,7 +2545,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="3"/>
+      <c r="O31" s="8">
+        <f t="shared" si="16"/>
+        <v>0.59665427509293667</v>
+      </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -2523,7 +2640,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.13015891969345006</v>
       </c>
       <c r="J32" s="10" t="e">
@@ -2546,7 +2663,10 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="3"/>
+      <c r="O32" s="10">
+        <f t="shared" si="16"/>
+        <v>0.17986609675286425</v>
+      </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -2626,27 +2746,27 @@
         <v>47</v>
       </c>
       <c r="C33" s="8" t="e">
-        <f t="shared" ref="C33:H33" si="17">+C11/C9</f>
+        <f t="shared" ref="C33:H33" si="18">+C11/C9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="8" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42086399918948053</v>
       </c>
       <c r="F33" s="8" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.40699263732822094</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.41472210072332699</v>
       </c>
       <c r="I33" s="8">
@@ -2654,26 +2774,29 @@
         <v>0.41548645295553688</v>
       </c>
       <c r="J33" s="8" t="e">
-        <f t="shared" ref="J33:N33" si="18">+J11/J9</f>
+        <f t="shared" ref="J33:N33" si="19">+J11/J9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.4087680250896964</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.40434168157423966</v>
       </c>
       <c r="M33" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N33" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O33" s="3"/>
+      <c r="O33" s="8">
+        <f t="shared" ref="O33" si="20">+O11/O9</f>
+        <v>0.54727023286010024</v>
+      </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -2753,27 +2876,27 @@
         <v>48</v>
       </c>
       <c r="C34" s="8" t="e">
-        <f t="shared" ref="C34:H34" si="19">+C15/C9</f>
+        <f t="shared" ref="C34:H34" si="21">+C15/C9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.14968918028990533</v>
       </c>
       <c r="F34" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.10272981873018806</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>8.9522932730783711E-2</v>
       </c>
       <c r="I34" s="8">
@@ -2781,26 +2904,29 @@
         <v>0.11938688117821268</v>
       </c>
       <c r="J34" s="8" t="e">
-        <f t="shared" ref="J34:N34" si="20">+J15/J9</f>
+        <f t="shared" ref="J34:N34" si="22">+J15/J9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>9.6649889618343227E-2</v>
       </c>
       <c r="L34" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-7.2017889087656592E-2</v>
       </c>
       <c r="M34" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N34" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O34" s="3"/>
+      <c r="O34" s="8">
+        <f t="shared" ref="O34" si="23">+O15/O9</f>
+        <v>0.15119063659860116</v>
+      </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -2880,27 +3006,27 @@
         <v>49</v>
       </c>
       <c r="C35" s="8" t="e">
-        <f t="shared" ref="C35:H35" si="21">+C18/C17</f>
+        <f t="shared" ref="C35:H35" si="24">+C18/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="8" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E35" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.23094731868651092</v>
       </c>
       <c r="F35" s="8" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.23565633522581086</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.23383032992555416</v>
       </c>
       <c r="I35" s="8">
@@ -2908,26 +3034,29 @@
         <v>0.25520545421042934</v>
       </c>
       <c r="J35" s="8" t="e">
-        <f t="shared" ref="J35:N35" si="22">+J18/J17</f>
+        <f t="shared" ref="J35:N35" si="25">+J18/J17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.24053894860845237</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-0.11238182810838757</v>
       </c>
       <c r="M35" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N35" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O35" s="3"/>
+      <c r="O35" s="8">
+        <f t="shared" ref="O35" si="26">+O18/O17</f>
+        <v>0.24694913650840364</v>
+      </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
